--- a/Data/collapsed database manual cases/durango_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/durango_collapsed_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E3DAFA-F740-4643-9332-5838B6666EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F8F079-1745-F04F-9248-83AF1B5D8F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="500" windowWidth="25480" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="778">
   <si>
     <t>uniqueid</t>
   </si>
@@ -2354,6 +2354,9 @@
   </si>
   <si>
     <t>SALVADOR CARRASCO SAENZ PARDO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS COVARRUBIAS FAUDOA</t>
   </si>
 </sst>
 </file>
@@ -2424,7 +2427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2435,7 +2438,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2742,7 +2744,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S348"/>
+  <dimension ref="A1:S349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -18123,7 +18125,7 @@
       <c r="E347" t="s">
         <v>379</v>
       </c>
-      <c r="F347" s="6" t="s">
+      <c r="F347" t="s">
         <v>776</v>
       </c>
       <c r="G347" s="5"/>
@@ -18149,6 +18151,23 @@
       </c>
       <c r="H348" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>10010</v>
+      </c>
+      <c r="B349">
+        <v>2025</v>
+      </c>
+      <c r="E349" t="s">
+        <v>102</v>
+      </c>
+      <c r="F349" t="s">
+        <v>777</v>
+      </c>
+      <c r="H349" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
